--- a/docs/testplan.xlsx
+++ b/docs/testplan.xlsx
@@ -1,39 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinavchatrathi/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A487F58F-CD95-234C-BE89-A630A332A12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="533">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -1183,75 +1161,572 @@
   </si>
   <si>
     <t>Game should pause/stop. Should navigate back to Balloon Selection screen</t>
+  </si>
+  <si>
+    <t>App launched, login completed, game screen loaded</t>
+  </si>
+  <si>
+    <t>1. Observe header shows language toggle switch 2. Default language is Hindi 3. Header subtitle shows 'वर्णमाला पज़ल' 4. Label shows 'Language: Hindi - हिंदी'</t>
+  </si>
+  <si>
+    <t>Hindi is default language. Toggle switch shows pink/purple gradient. All grid slots and letter bank display Hindi consonants (क to ज्ञ). UI and content assets reflect Hindi.</t>
+  </si>
+  <si>
+    <t>App launched, login completed</t>
+  </si>
+  <si>
+    <t>1. Enter name and click 'Start Playing!' 2. Observe game initializes with age-appropriate consonant puzzle (36 letters)</t>
+  </si>
+  <si>
+    <t>Game loads directly into the alphabet-level consonant puzzle with 36 drop slots and 36 shuffled letter tiles. Content is designed for ages 4-5 with large tiles, bright colors, and audio feedback.</t>
+  </si>
+  <si>
+    <t>Game active, Hindi selected, 36 shuffled tiles in bank</t>
+  </si>
+  <si>
+    <t>1. Drag letter 'क' from bank to slot 1 2. Drag letter 'ख' from bank to slot 2 3. Drag a wrong letter (e.g., 'म') to slot 3</t>
+  </si>
+  <si>
+    <t>Correct drops: letter appears in slot with green pop-in animation, tile removed from bank, score increments (1/36, 2/36). Wrong drop: slot shakes red for 600ms, letter stays in bank, score unchanged.</t>
+  </si>
+  <si>
+    <t>Level 1 (Alphabet Game) completed</t>
+  </si>
+  <si>
+    <t>1. Complete all 36 consonants in Varnamala Puzzle 2. Observe completion banner with final score and time</t>
+  </si>
+  <si>
+    <t>Game completion acts as prerequisite checkpoint. Completion banner displays '🎉 Great job! शाबाश!' confirming L1 mastery before word-based levels.</t>
+  </si>
+  <si>
+    <t>Level 1 completed, Level 2 completed</t>
+  </si>
+  <si>
+    <t>1. Complete Hindi Varnamala Puzzle 2. Toggle to Telugu 3. Complete Telugu Varnamala Puzzle</t>
+  </si>
+  <si>
+    <t>Both Hindi and Telugu alphabet puzzles can be completed independently. System tracks completion for each language, verifying alphabet mastery in both languages.</t>
+  </si>
+  <si>
+    <t>Game active, multiple consonants placed</t>
+  </si>
+  <si>
+    <t>1. Place 18 correct consonants (half of 36) 2. Observe progress at 50% 3. Continue placing remaining 18 consonants</t>
+  </si>
+  <si>
+    <t>Progress bar tracks from 0% to 50% to 100%. All 36 consonants including conjuncts (क्ष, त्र, ज्ञ) can be placed correctly. Game handles multi-character conjuncts properly.</t>
+  </si>
+  <si>
+    <t>Play Sentence Game (L5)</t>
+  </si>
+  <si>
+    <t>Game active, grid visible</t>
+  </si>
+  <si>
+    <t>1. Observe 8-row grid layout: rows of [5,5,5,5,5,4,4,3] 2. Place consonants following the traditional Varnamala sequence 3. Verify complete Varnamala order</t>
+  </si>
+  <si>
+    <t>Grid follows traditional grouping: 5 Varga groups (5 each), semi-vowels य र ल व (4), sibilants श ष स ह (4), conjuncts क्ष त्र ज्ञ (3). Total 36 slots in correct Varnamala order.</t>
+  </si>
+  <si>
+    <t>All 36 consonants placed, game completed</t>
+  </si>
+  <si>
+    <t>1. Complete the puzzle in approximately 60 seconds 2. Observe final score on completion banner 3. Complete again in 120 seconds and compare</t>
+  </si>
+  <si>
+    <t>Final Score = (36 / time_in_seconds) × 100. At 60s → score 60, at 120s → score 30. Faster completion earns higher points. Score displayed on completion banner as 'Final Score: X'.</t>
+  </si>
+  <si>
+    <t>Game active, no consonants placed yet</t>
+  </si>
+  <si>
+    <t>1. Try to observe locked/unlocked state 2. Place consonants sequentially from slot 1 to 36 3. Complete all 36 to unlock completion</t>
+  </si>
+  <si>
+    <t>Slots accept only the correct consonant for that position. Progress is sequential — score increments only on correct placement. Completion (36/36) unlocks the celebration banner and confetti.</t>
+  </si>
+  <si>
+    <t>Game active, stats bar visible at top of puzzle board</t>
+  </si>
+  <si>
+    <t>1. Observe stats bar showing ⏱️ timer, ⭐ score, and progress bar 2. Place 10 correct consonants 3. Observe updated stats</t>
+  </si>
+  <si>
+    <t>Timer shows elapsed time in MM:SS format. Score updates to 10/36. Progress bar fills to ~28% with green-to-blue gradient and percentage text. All stats update in real-time.</t>
+  </si>
+  <si>
+    <t>Game active, letter bank visible with tiles showing 🔊 icon</t>
+  </si>
+  <si>
+    <t>1. Click on letter tile 'प' in the bank — listen for pronunciation 2. Drag correct letter 'क' to slot 1 — listen for pronunciation on drop</t>
+  </si>
+  <si>
+    <t>Click: SpeechSynthesis pronounces letter at rate 0.75, pitch 1.1 in Hindi (hi-IN). Correct drop: same pronunciation plays automatically. Both trigger clear native audio feedback for language acquisition.</t>
+  </si>
+  <si>
+    <t>Game loaded in Hindi mode, toggle visible in header</t>
+  </si>
+  <si>
+    <t>1. Click language toggle in header 2. Observe all content switches to Telugu 3. Click toggle again to switch back to Hindi</t>
+  </si>
+  <si>
+    <t>Toggle to Telugu: grid shows Telugu consonants (క to జ్ఞ), bank shows shuffled Telugu tiles, subtitle shows 'వర్ణమాల పజిల్', speech uses te-IN. Toggle back: Hindi content restored with preserved progress. Both languages fully functional.</t>
+  </si>
+  <si>
+    <t>Select Language (UC-1)</t>
+  </si>
+  <si>
+    <t>App launched, language selection screen visible</t>
+  </si>
+  <si>
+    <t>1. Open the app 2. Select "Hindi" as the learning language 3. Navigate to Crossword Hub</t>
+  </si>
+  <si>
+    <t>Language is set to Hindi (hi). All crossword clues, words, and letter bank display Hindi content. Setting persists across all game levels.</t>
+  </si>
+  <si>
+    <t>Toggle Telugu Content (UC-12)</t>
+  </si>
+  <si>
+    <t>1. Open the app 2. Select "Telugu" as the learning language 3. Navigate to Crossword Hub 4. Start Level 1</t>
+  </si>
+  <si>
+    <t>Language is set to Telugu (te). Crossword words show Telugu script (e.g. "పండు" for fruit, "నీరు" for water). Letter bank contains Telugu graphemes only.</t>
+  </si>
+  <si>
+    <t>Invalid Language Rejection</t>
+  </si>
+  <si>
+    <t>API endpoint accessible</t>
+  </si>
+  <si>
+    <t>1. Call GET /api/crossword/data/fr/1 with unsupported language code "fr"</t>
+  </si>
+  <si>
+    <t>API returns 400 status with error: "Language must be 'hi' or 'te'." Game does not load.</t>
+  </si>
+  <si>
+    <t>Play Crossword Level 1 (UC-3)</t>
+  </si>
+  <si>
+    <t>Language selected (Hindi), Level 1 unlocked</t>
+  </si>
+  <si>
+    <t>1. Navigate to Crossword Hub 2. Select Level 1 3. Click "Start Game" 4. Observe the 4×4 grid, clue panel, and letter bank</t>
+  </si>
+  <si>
+    <t>4×4 grid renders with active cells. Clue panel shows emoji clues (🍎, 🏠, 💧, 🐱). Letter bank displays shuffled Hindi letters. Each word has orientation (across/down) and 10-point reward.</t>
+  </si>
+  <si>
+    <t>Place Correct Letter in Cell</t>
+  </si>
+  <si>
+    <t>Level 1 game active, grid and letter bank visible</t>
+  </si>
+  <si>
+    <t>1. Click on an empty grid cell 2. Pick the correct letter from the letter bank 3. Letter appears in cell</t>
+  </si>
+  <si>
+    <t>Cell fills with selected letter. Letter is consumed from the bank. Cell status changes from idle. If all cells of a word are filled correctly, word is marked complete, score +10, and TTS speaks the word.</t>
+  </si>
+  <si>
+    <t>Complete All Words in a Level</t>
+  </si>
+  <si>
+    <t>Level 1 game active, 3 of 4 words already solved</t>
+  </si>
+  <si>
+    <t>1. Place the final correct letters for the last remaining word 2. All 4 words now solved</t>
+  </si>
+  <si>
+    <t>Level complete overlay appears with congratulatory message ("शाबाश!" for Hindi / "బాగా చేశావు!" for Telugu). Score and completed words saved to backend. Level marked as completed.</t>
+  </si>
+  <si>
+    <t>Level Progression — Different Words Per Level (UC-4/5/6)</t>
+  </si>
+  <si>
+    <t>Level 1 completed</t>
+  </si>
+  <si>
+    <t>1. Return to Crossword Hub 2. Select Level 2 3. Start game and observe words</t>
+  </si>
+  <si>
+    <t>Level 2 loads a different set of words (Tea, Milk, Lotus, Roti) than Level 1 (Fruit, Home, Water, Cat). Grid layout and clues are unique per level.</t>
+  </si>
+  <si>
+    <t>Earn Reward Points (UC-8)</t>
+  </si>
+  <si>
+    <t>A crossword level just completed with all words solved</t>
+  </si>
+  <si>
+    <t>1. Complete Level 1 with all 4 words correct (score = 40) 2. Observe progress save confirmation</t>
+  </si>
+  <si>
+    <t>Progress saved successfully: score=40, completed=true, completedWords contains all 4 word IDs, attempts=1. Points displayed on Level Select screen.</t>
+  </si>
+  <si>
+    <t>Best Score Persistence on Replay</t>
+  </si>
+  <si>
+    <t>Level 1 completed with score 40</t>
+  </si>
+  <si>
+    <t>1. Replay Level 1 2. Complete with lower score (e.g. 20) 3. Check progress on Level Select</t>
+  </si>
+  <si>
+    <t>Best score retained → Math.max(40, 20) = 40. Score never downgrades. Attempts count increments to 2. completed stays true.</t>
+  </si>
+  <si>
+    <t>Unlock Content Sequence (UC-9)</t>
+  </si>
+  <si>
+    <t>New user, no levels completed</t>
+  </si>
+  <si>
+    <t>1. Open Crossword Hub 2. Observe level buttons — Level 1 shows ☆, Levels 2-5 show 🔒 3. Try clicking Level 2</t>
+  </si>
+  <si>
+    <t>Level 1 is clickable and playable. Levels 2-5 are locked (disabled, show 🔒). Clicking a locked level does nothing. Message: "Complete Level 1 to unlock this level!"</t>
+  </si>
+  <si>
+    <t>Level Unlock After Completion</t>
+  </si>
+  <si>
+    <t>Level 1 just completed</t>
+  </si>
+  <si>
+    <t>1. Return to Crossword Hub after completing Level 1 2. Observe Level 2 status 3. Click Level 2 4. Click "Start Game"</t>
+  </si>
+  <si>
+    <t>Level 1 shows ⭐ (completed with score). Level 2 is now unlocked (☆). Levels 3-5 remain 🔒. Level 2 game loads correctly when started.</t>
+  </si>
+  <si>
+    <t>View Progress Dashboard (UC-10)</t>
+  </si>
+  <si>
+    <t>Levels 1 and 2 completed, Level 3 in progress</t>
+  </si>
+  <si>
+    <t>1. Open Crossword Hub 2. Observe all level cards</t>
+  </si>
+  <si>
+    <t>Level 1: ⭐ + score displayed. Level 2: ⭐ + score displayed. Level 3: ☆ (unlocked, selectable). Levels 4-5: 🔒 (locked). Words Completed count shown (e.g. "3/4").</t>
+  </si>
+  <si>
+    <t>New User Default Progress (UC-10)</t>
+  </si>
+  <si>
+    <t>Brand new user, never played</t>
+  </si>
+  <si>
+    <t>1. Open Crossword Hub 2. Fetch progress from API</t>
+  </si>
+  <si>
+    <t>API returns default progress for all 5 levels: each with score=0, completed=false, completedWords=[]. Level 1 auto-selected as first playable.</t>
+  </si>
+  <si>
+    <t>Audio Pronunciation (UC-11)</t>
+  </si>
+  <si>
+    <t>Crossword game active, a word just completed</t>
+  </si>
+  <si>
+    <t>1. Complete a word (e.g. "फल") in the grid 2. Listen for audio feedback</t>
+  </si>
+  <si>
+    <t>TTS (Text-to-Speech) speaks the completed word aloud using the browser SpeechSynthesis API in the selected language (hi/te). Provides auditory reinforcement for language acquisition.</t>
+  </si>
+  <si>
+    <t>Save Progress Validation — Missing Fields</t>
+  </si>
+  <si>
+    <t>1. POST /api/crossword/save-progress with body { userId: "kid1" } (missing score and completed fields)</t>
+  </si>
+  <si>
+    <t>API returns 400 status with error: "userId, score (number), and completed (boolean) are required." No progress record is created or modified.</t>
+  </si>
+  <si>
+    <t>UC-3: Play Alphabet Game — API Load</t>
+  </si>
+  <si>
+    <t>Backend running, /api/swaras accessible</t>
+  </si>
+  <si>
+    <t>1. Open Swara Sing-Along Game 2. Observe screen</t>
+  </si>
+  <si>
+    <t>Loading spinner appears with text "लोड हो रहा है..." and "Loading swaras from database". API returns all 13 swaras sorted by id. Welcome screen appears after load.</t>
+  </si>
+  <si>
+    <t>UC-3: Welcome Screen Before Start</t>
+  </si>
+  <si>
+    <t>Swaras loaded successfully</t>
+  </si>
+  <si>
+    <t>1. Observe the welcome screen before pressing Start</t>
+  </si>
+  <si>
+    <t>Screen shows 🎵 emoji, title "Sing-Along Swara Song!", subtitle "Learn all 13 Hindi vowels / हिंदी के सभी 13 स्वर सीखो!". Only "▶ Start!" button visible. Progress bar shows but inert.</t>
+  </si>
+  <si>
+    <t>UC-3: Controls Disabled Before Start</t>
+  </si>
+  <si>
+    <t>Welcome screen visible</t>
+  </si>
+  <si>
+    <t>1. Observe ⏮ Prev, ⏭ Next, 🔁 Replay buttons</t>
+  </si>
+  <si>
+    <t>All navigation buttons (Prev, Next, Replay) are disabled (greyed) before the game starts — because isStarted = false. Only "▶ Start!" and Mute are active.</t>
+  </si>
+  <si>
+    <t>UC-3: Start Game — First Vowel Plays</t>
+  </si>
+  <si>
+    <t>Welcome screen showing</t>
+  </si>
+  <si>
+    <t>1. Click "▶ Start!"</t>
+  </si>
+  <si>
+    <t>Game resets to index 0 ('अ'). Entry animation triggers ('entering' → 'playing' after 600ms). After 400ms delay, audio 'a_se_amarood.mp3' plays. Letter 'अ', image of 'अमरूद', word 'अमरूद', phrase 'अ से अमरूद' displayed.</t>
+  </si>
+  <si>
+    <t>UC-11: Audio Pronunciation</t>
+  </si>
+  <si>
+    <t>Game started, on vowel 'अ'</t>
+  </si>
+  <si>
+    <t>1. Wait for audio to play automatically 2. Listen</t>
+  </si>
+  <si>
+    <t>Audio file for current vowel plays aloud. Any previous audio is stopped before new audio starts. Audio plays at browser native volume (no mute).</t>
+  </si>
+  <si>
+    <t>UC-3: Auto-Advance After Audio</t>
+  </si>
+  <si>
+    <t>Game playing, on vowel 'अ'</t>
+  </si>
+  <si>
+    <t>1. Let 'अ' audio finish completely without pressing anything</t>
+  </si>
+  <si>
+    <t>After audio ends: if autoPlayEnabled=true, game auto-advances to index 1 ('आ'). Entry animation triggers. Next audio ('aa_se_aam.mp3') plays after 400ms. No user action needed.</t>
+  </si>
+  <si>
+    <t>UC-3: Manual Next Button</t>
+  </si>
+  <si>
+    <t>Game playing, on vowel 'आ' (index 1)</t>
+  </si>
+  <si>
+    <t>1. Click "⏭ Next" button</t>
+  </si>
+  <si>
+    <t>Current audio stops immediately. Index advances to 'इ' (index 2). Entry animation plays. Since isPlaying=true and autoPlayEnabled=true, next audio plays automatically after 400ms.</t>
+  </si>
+  <si>
+    <t>UC-3: Manual Prev Button</t>
+  </si>
+  <si>
+    <t>Game playing, on vowel 'इ' (index 2)</t>
+  </si>
+  <si>
+    <t>1. Click "⏮ Prev" button</t>
+  </si>
+  <si>
+    <t>Current audio stops. Index moves back to 'आ' (index 1). Entry animation plays. Since isPlaying=true, previous vowel's audio plays automatically after 400ms.</t>
+  </si>
+  <si>
+    <t>UC-3: Boundary — Prev Disabled at First</t>
+  </si>
+  <si>
+    <t>Game started, currently on index 0 ('अ')</t>
+  </si>
+  <si>
+    <t>1. Observe ⏮ Prev button</t>
+  </si>
+  <si>
+    <t>"⏮ Prev" button is disabled (canGoPrev = currentIndex &gt; 0 = false). Clicking nothing happens. Game stays on 'अ'.</t>
+  </si>
+  <si>
+    <t>UC-3: Boundary — Next Disabled at Last</t>
+  </si>
+  <si>
+    <t>Game auto-played to final vowel (index 12, 'अः')</t>
+  </si>
+  <si>
+    <t>1. Observe ⏭ Next button</t>
+  </si>
+  <si>
+    <t>"⏭ Next" button is disabled (canGoNext = currentIndex &lt; swaraList.length - 1 = false). Game waits for audio to finish before triggering completion.</t>
+  </si>
+  <si>
+    <t>UC-3: Pause Button</t>
+  </si>
+  <si>
+    <t>Game is auto-playing vowel 'ऋ' (index 6)</t>
+  </si>
+  <si>
+    <t>1. Click "⏸ Pause" button during playback</t>
+  </si>
+  <si>
+    <t>Audio pauses. autoPlayEnabled.current set to false. Animation class clears. Button changes to "▶ Play". Game stays on 'ऋ'. Auto-advance stopped.</t>
+  </si>
+  <si>
+    <t>UC-3: Resume After Pause</t>
+  </si>
+  <si>
+    <t>Game paused on vowel 'ऋ'</t>
+  </si>
+  <si>
+    <t>1. Click "▶ Play" button</t>
+  </si>
+  <si>
+    <t>autoPlayEnabled.current set to true. isPlaying = true. Button changes back to "⏸ Pause". If audio ref still exists, it resumes; if lost, current vowel audio plays fresh.</t>
+  </si>
+  <si>
+    <t>UC-11: Replay Current Vowel</t>
+  </si>
+  <si>
+    <t>Game on vowel 'ए' (index 7), audio just ended</t>
+  </si>
+  <si>
+    <t>1. Click "🔁 Replay" button</t>
+  </si>
+  <si>
+    <t>Current audio stops. Entry animation triggers. After 300ms delay, audio for 'ए' ('e_se_edi.mp3') plays again from beginning. Vowel does not change.</t>
+  </si>
+  <si>
+    <t>UC-11: Mute / Unmute</t>
+  </si>
+  <si>
+    <t>Game playing audio for any vowel</t>
+  </si>
+  <si>
+    <t>1. Click "🔊 Mute" button 2. Let 2 vowels play 3. Click "🔇 Unmute"</t>
+  </si>
+  <si>
+    <t>Mute: audio silenced but auto-play continues (animation + auto-advance still work). Button shows 🔇 + label "Unmute". Unmute: audio becomes audible again. Button shows 🔊 + label "Mute".</t>
+  </si>
+  <si>
+    <t>UC-3: Completion After All 13 Vowels</t>
+  </si>
+  <si>
+    <t>Game on last vowel 'अः' (index 12)</t>
+  </si>
+  <si>
+    <t>1. Let final vowel's audio finish completely</t>
+  </si>
+  <si>
+    <t>autoPlayEnabled.current = false. isCompleted = true. Completion screen renders: 5 stars (⭐🌟⭐🌟⭐), 🎉 emoji, "Well Done! Great Job! 🎊", "You learned all 13 Hindi vowels! / तुमने सभी 13 स्वर सीख लिए!". "🔁 Play Again!" button visible.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="16">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF0000D4"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Liberation Serif"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Noto Sans Arabic UI"/>
+      <name val="Noto Sans Arabic"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <color rgb="FFCCCCCC"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Ui-monospace"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFCCCCCC"/>
+      <name val="System-ui"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="10">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1265,7 +1740,6 @@
       <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1274,11 +1748,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1293,75 +1765,216 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6B7280"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6B7280"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6B7280"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6B7280"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6B7280"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF6B7280"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6B7280"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF6B7280"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6B7280"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6B7280"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6B7280"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF6B7280"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="47">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="5" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1551,2588 +2164,4454 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U161"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
-    <col min="2" max="2" width="31.1640625" customWidth="1"/>
-    <col min="3" max="3" width="109" customWidth="1"/>
-    <col min="4" max="4" width="209.6640625" customWidth="1"/>
-    <col min="5" max="5" width="206" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="16.13"/>
+    <col customWidth="1" min="2" max="2" width="31.13"/>
+    <col customWidth="1" min="3" max="3" width="109.0"/>
+    <col customWidth="1" min="4" max="4" width="209.63"/>
+    <col customWidth="1" min="5" max="5" width="206.0"/>
+    <col customWidth="1" min="6" max="6" width="21.5"/>
+    <col customWidth="1" min="7" max="7" width="19.13"/>
+    <col customWidth="1" min="8" max="8" width="24.0"/>
+    <col customWidth="1" min="9" max="9" width="23.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" ht="13">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" ht="13">
-      <c r="A4" s="9">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="F3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9" ht="13">
-      <c r="A5" s="9">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="F4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9" ht="13">
-      <c r="A6" s="9">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="F5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" spans="1:9" ht="13">
-      <c r="A7" s="9">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="F6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="1:9" ht="13">
-      <c r="A8" s="9">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" ht="13">
-      <c r="A9" s="9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="F8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" ht="13">
-      <c r="A10" s="9">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" ht="13">
-      <c r="A11" s="9">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="F10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="1:9" ht="13">
-      <c r="A12" s="9">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="F11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>10.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9" ht="13">
-      <c r="A13" s="9">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="F12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>11.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" ht="13">
-      <c r="A14" s="9">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="F13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>12.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" ht="13">
-      <c r="A15" s="9">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="F14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>13.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" ht="13">
-      <c r="A16" s="9">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="F15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>14.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="1:21" ht="13">
-      <c r="A17" s="9">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="F16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>15.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="1:21" ht="13">
-      <c r="A18" s="9">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="F17" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>16.0</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="1:21" ht="13">
-      <c r="A19" s="9">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="F18" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>17.0</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:21" ht="13">
-      <c r="A20" s="9">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="F19" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>18.0</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:21" ht="13">
-      <c r="A21" s="9">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="F20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>19.0</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="1:21" ht="13">
-      <c r="A22" s="9">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>20.0</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="1:21" ht="17.25" customHeight="1">
-      <c r="A23" s="9">
-        <v>21</v>
-      </c>
-      <c r="B23" s="11" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
+      <c r="A23" s="10">
+        <v>21.0</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-    </row>
-    <row r="24" spans="1:21" ht="22.5" customHeight="1">
-      <c r="A24" s="9">
-        <v>22</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="F23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="10">
+        <v>22.0</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-    </row>
-    <row r="25" spans="1:21" ht="15">
-      <c r="A25" s="9">
-        <v>23</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="F24" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>23.0</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-    </row>
-    <row r="26" spans="1:21" ht="18" customHeight="1">
-      <c r="A26" s="9">
-        <v>24</v>
-      </c>
-      <c r="B26" s="11" t="s">
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+    </row>
+    <row r="26" ht="18.0" customHeight="1">
+      <c r="A26" s="10">
+        <v>24.0</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-    </row>
-    <row r="27" spans="1:21" ht="24.75" customHeight="1">
-      <c r="A27" s="9">
-        <v>25</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="F26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+    </row>
+    <row r="27" ht="24.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>25.0</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-    </row>
-    <row r="28" spans="1:21" ht="18.75" customHeight="1">
-      <c r="A28" s="9">
-        <v>26</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="F27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>26.0</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
-    </row>
-    <row r="29" spans="1:21" ht="15">
-      <c r="A29" s="9">
-        <v>27</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="F28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>27.0</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-    </row>
-    <row r="30" spans="1:21" ht="20.25" customHeight="1">
-      <c r="A30" s="9">
-        <v>28</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="F29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+    </row>
+    <row r="30" ht="20.25" customHeight="1">
+      <c r="A30" s="10">
+        <v>28.0</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-    </row>
-    <row r="31" spans="1:21" ht="21.75" customHeight="1">
-      <c r="A31" s="9">
-        <v>29</v>
-      </c>
-      <c r="B31" s="11" t="s">
+      <c r="F30" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+    </row>
+    <row r="31" ht="21.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>29.0</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
-    </row>
-    <row r="32" spans="1:21" ht="15">
-      <c r="A32" s="12">
-        <v>30</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="13">
+        <v>30.0</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
-    </row>
-    <row r="33" spans="1:21" ht="17.25" customHeight="1">
-      <c r="A33" s="12">
-        <v>31</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="F32" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
+      <c r="A33" s="13">
+        <v>31.0</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-    </row>
-    <row r="34" spans="1:21" ht="20.25" customHeight="1">
-      <c r="A34" s="12">
-        <v>32</v>
-      </c>
-      <c r="B34" s="11" t="s">
+      <c r="F33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+    </row>
+    <row r="34" ht="20.25" customHeight="1">
+      <c r="A34" s="13">
+        <v>32.0</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="11"/>
-    </row>
-    <row r="35" spans="1:21" ht="13">
-      <c r="A35" s="12">
-        <f t="shared" ref="A35:A37" si="0">A34+1</f>
+      <c r="F34" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="12"/>
+      <c r="U34" s="12"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="13">
+        <f t="shared" ref="A35:A37" si="1">A34+1</f>
         <v>33</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="13">
-      <c r="A36" s="12">
-        <f t="shared" si="0"/>
+      <c r="F35" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="13">
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="F36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="13">
-      <c r="A37" s="12">
-        <f t="shared" si="0"/>
+      <c r="F36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="13">
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="13">
-      <c r="D38" s="13" t="s">
+      <c r="F37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="D38" s="14" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="13">
-      <c r="D39" s="13" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="D39" s="14" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="13">
-      <c r="D40" s="13" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="D40" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="13">
-      <c r="D41" s="13" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="D41" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="13">
-      <c r="D42" s="13" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="D42" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="13">
-      <c r="D43" s="13" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="D43" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="13">
-      <c r="A44" s="12">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="13">
         <f>A37+1</f>
         <v>36</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="F44" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="13">
-      <c r="D45" s="13" t="s">
+      <c r="F44" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="D45" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="13">
-      <c r="D46" s="13" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="D46" s="14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="13">
-      <c r="D47" s="13" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="D47" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="13">
-      <c r="D48" s="13" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="D48" s="14" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13">
-      <c r="D49" s="13" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="D49" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13">
-      <c r="D50" s="13" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="D50" s="14" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13">
-      <c r="A51" s="12">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="13">
         <f>A44+1</f>
         <v>37</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="F51" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="13">
-      <c r="D52" s="13" t="s">
+      <c r="F51" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="D52" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13">
-      <c r="D53" s="13" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="D53" s="14" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="13">
-      <c r="D54" s="13" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="D54" s="14" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="13">
-      <c r="D55" s="13" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="D55" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="13">
-      <c r="D56" s="13" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="D56" s="14" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13">
-      <c r="D57" s="13" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="D57" s="14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13">
-      <c r="A58" s="12">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="13">
         <f>A51+1</f>
         <v>38</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="13">
-      <c r="D59" s="13" t="s">
+      <c r="F58" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="D59" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="E59" s="14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13">
-      <c r="D60" s="13" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="D60" s="14" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13">
-      <c r="D61" s="13" t="s">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="D61" s="14" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13">
-      <c r="D62" s="13" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="D62" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13">
-      <c r="D63" s="13" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="D63" s="14" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13">
-      <c r="A64" s="12">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="13">
         <f>A58+1</f>
         <v>39</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="H64" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="13">
-      <c r="D65" s="13" t="s">
+      <c r="H64" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="D65" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="E65" s="14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13">
-      <c r="D66" s="13" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="D66" s="14" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13">
-      <c r="D67" s="13" t="s">
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="D67" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13">
-      <c r="D68" s="13" t="s">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="D68" s="14" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13">
-      <c r="D69" s="13" t="s">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="D69" s="14" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13">
-      <c r="D70" s="13" t="s">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="D70" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13">
-      <c r="A71" s="12">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="13">
         <f>A64+1</f>
         <v>40</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E71" s="13" t="s">
+      <c r="E71" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="F71" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="13">
-      <c r="D72" s="13" t="s">
+      <c r="F71" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="D72" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E72" s="13" t="s">
+      <c r="E72" s="14" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13">
-      <c r="D73" s="13" t="s">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="D73" s="14" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="13">
-      <c r="D74" s="13" t="s">
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="D74" s="14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="13">
-      <c r="D75" s="13" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="D75" s="14" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="13">
-      <c r="D76" s="13" t="s">
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="D76" s="14" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="13">
-      <c r="A77" s="12">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="13">
         <f>A71+1</f>
         <v>41</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F77" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="13">
-      <c r="D78" s="13" t="s">
+      <c r="F77" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="D78" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="14" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="13">
-      <c r="D79" s="13" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="D79" s="14" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="13">
-      <c r="D80" s="13" t="s">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="D80" s="14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="13">
-      <c r="D81" s="13" t="s">
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="D81" s="14" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="13">
-      <c r="D82" s="13" t="s">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="D82" s="14" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="13">
-      <c r="A83" s="12">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="13">
         <f>A77+1</f>
         <v>42</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="E83" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="F83" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="13">
-      <c r="D84" s="13" t="s">
+      <c r="F83" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="D84" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="E84" s="14" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="13">
-      <c r="D85" s="13" t="s">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="D85" s="14" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="13">
-      <c r="D86" s="13" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="D86" s="14" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="13">
-      <c r="D87" s="13" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="D87" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="13">
-      <c r="D88" s="13" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="D88" s="14" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="13">
-      <c r="D89" s="13" t="s">
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="D89" s="14" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="13">
-      <c r="A90" s="12">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="13">
         <f>A83+1</f>
         <v>43</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="E90" s="13" t="s">
+      <c r="E90" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="F90" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="13">
-      <c r="D91" s="13" t="s">
+      <c r="F90" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="D91" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E91" s="13" t="s">
+      <c r="E91" s="14" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="13">
-      <c r="D92" s="13" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="D92" s="14" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="13">
-      <c r="D93" s="13" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="D93" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="13">
-      <c r="D94" s="13" t="s">
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="D94" s="14" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="13">
-      <c r="D95" s="13" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="D95" s="14" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="13">
-      <c r="D96" s="13" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="D96" s="14" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="13">
-      <c r="D97" s="13" t="s">
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="D97" s="14" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="13">
-      <c r="A98" s="12">
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="13">
         <f>A44+1</f>
         <v>37</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="E98" s="13" t="s">
+      <c r="E98" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="F98" s="13" t="s">
+      <c r="F98" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="H98" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="13">
-      <c r="D99" s="13" t="s">
+      <c r="H98" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="D99" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="E99" s="13" t="s">
+      <c r="E99" s="14" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="13">
-      <c r="D100" s="13" t="s">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="D100" s="14" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="13">
-      <c r="D101" s="13" t="s">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="D101" s="14" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="13">
-      <c r="D102" s="13" t="s">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="D102" s="14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="13">
-      <c r="D103" s="13" t="s">
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="D103" s="14" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="13">
-      <c r="D104" s="13" t="s">
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="D104" s="14" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="13">
-      <c r="D105" s="13" t="s">
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="D105" s="14" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="13">
-      <c r="A106" s="12">
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="13">
         <f>A98+1</f>
         <v>38</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E106" s="13" t="s">
+      <c r="E106" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="F106" s="13" t="s">
+      <c r="F106" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="H106" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="13">
-      <c r="D107" s="13" t="s">
+      <c r="H106" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="D107" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="E107" s="13" t="s">
+      <c r="E107" s="14" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="13">
-      <c r="D108" s="13" t="s">
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="D108" s="14" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="13">
-      <c r="D109" s="13" t="s">
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="D109" s="14" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="13">
-      <c r="D110" s="13" t="s">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="D110" s="14" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="13">
-      <c r="D111" s="13" t="s">
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="D111" s="14" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="13">
-      <c r="D112" s="13" t="s">
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="D112" s="14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="13">
-      <c r="D113" s="13" t="s">
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="D113" s="14" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="13">
-      <c r="A114" s="12">
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="13">
         <f>A106+1</f>
         <v>39</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="E114" s="13" t="s">
+      <c r="E114" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="F114" s="13" t="s">
+      <c r="F114" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="H114" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="13">
-      <c r="D115" s="13" t="s">
+      <c r="H114" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="D115" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="E115" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="13">
-      <c r="D116" s="13" t="s">
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="D116" s="14" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="13">
-      <c r="D117" s="13" t="s">
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="D117" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="13">
-      <c r="D118" s="13" t="s">
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="D118" s="14" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="13">
-      <c r="D119" s="13" t="s">
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="D119" s="14" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="13">
-      <c r="D120" s="13" t="s">
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="D120" s="14" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="13">
-      <c r="D121" s="13" t="s">
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="D121" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="13">
-      <c r="A122" s="12">
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="13">
         <f>A114+1</f>
         <v>40</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="E122" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="F122" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="13">
-      <c r="A123" s="12">
-        <f t="shared" ref="A123:A153" si="1">A122+1</f>
+      <c r="F122" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" s="9"/>
+      <c r="H122" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="13">
+        <f t="shared" ref="A123:A153" si="2">A122+1</f>
         <v>41</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="E123" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="F123" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" s="10"/>
-      <c r="H123" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="13">
-      <c r="A124" s="12">
-        <f t="shared" si="1"/>
+      <c r="F123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="11"/>
+      <c r="H123" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="13">
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="E124" s="13" t="s">
+      <c r="E124" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="F124" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="13">
-      <c r="A125" s="12">
-        <f t="shared" si="1"/>
+      <c r="F124" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="13">
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E125" s="13" t="s">
+      <c r="E125" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="F125" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="13">
-      <c r="A126" s="12">
-        <f t="shared" si="1"/>
+      <c r="F125" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="13">
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="E126" s="13" t="s">
+      <c r="E126" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="F126" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="13">
-      <c r="A127" s="12">
-        <f t="shared" si="1"/>
+      <c r="F126" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G126" s="11"/>
+      <c r="H126" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="13">
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E127" s="13" t="s">
+      <c r="E127" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F127" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G127" s="10"/>
-      <c r="H127" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="13">
-      <c r="A128" s="12">
-        <f t="shared" si="1"/>
+      <c r="F127" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="13">
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="C128" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="E128" s="13" t="s">
+      <c r="E128" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="F128" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G128" s="10"/>
-      <c r="H128" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="13">
-      <c r="A129" s="12">
-        <f t="shared" si="1"/>
+      <c r="F128" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="13">
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D129" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="E129" s="13" t="s">
+      <c r="E129" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F129" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G129" s="10"/>
-      <c r="H129" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="13">
-      <c r="A130" s="12">
-        <f t="shared" si="1"/>
+      <c r="F129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="13">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C130" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="E130" s="13" t="s">
+      <c r="E130" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="F130" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="13">
-      <c r="A131" s="12">
-        <f t="shared" si="1"/>
+      <c r="F130" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="13">
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="C131" s="13" t="s">
+      <c r="C131" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="E131" s="13" t="s">
+      <c r="E131" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="F131" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="13">
-      <c r="A132" s="12">
-        <f t="shared" si="1"/>
+      <c r="F131" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="13">
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C132" s="13" t="s">
+      <c r="C132" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E132" s="13" t="s">
+      <c r="E132" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F132" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="13">
-      <c r="A133" s="12">
-        <f t="shared" si="1"/>
+      <c r="F132" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="13">
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C133" s="13" t="s">
+      <c r="C133" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="D133" s="13" t="s">
+      <c r="D133" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E133" s="13" t="s">
+      <c r="E133" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="F133" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="13">
-      <c r="A134" s="12">
-        <f t="shared" si="1"/>
+      <c r="F133" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="13">
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="C134" s="13" t="s">
+      <c r="C134" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D134" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="E134" s="13" t="s">
+      <c r="E134" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="F134" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G134" s="10"/>
-      <c r="H134" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="13">
-      <c r="A135" s="12">
-        <f t="shared" si="1"/>
+      <c r="F134" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G134" s="11"/>
+      <c r="H134" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="13">
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C135" s="13" t="s">
+      <c r="C135" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="D135" s="13" t="s">
+      <c r="D135" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E135" s="13" t="s">
+      <c r="E135" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G135" s="10"/>
-      <c r="H135" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="13">
-      <c r="A136" s="12">
-        <f t="shared" si="1"/>
+      <c r="F135" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G135" s="11"/>
+      <c r="H135" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="13">
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="C136" s="13" t="s">
+      <c r="C136" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="D136" s="13" t="s">
+      <c r="D136" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="E136" s="13" t="s">
+      <c r="E136" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="F136" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="10"/>
-      <c r="H136" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="13">
-      <c r="A137" s="12">
-        <f t="shared" si="1"/>
+      <c r="F136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="11"/>
+      <c r="H136" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="13">
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="D137" s="13" t="s">
+      <c r="D137" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E137" s="13" t="s">
+      <c r="E137" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="F137" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G137" s="10"/>
-      <c r="H137" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="13">
-      <c r="A138" s="12">
-        <f t="shared" si="1"/>
+      <c r="F137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" s="11"/>
+      <c r="H137" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="13">
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C138" s="13" t="s">
+      <c r="C138" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="D138" s="13" t="s">
+      <c r="D138" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="E138" s="13" t="s">
+      <c r="E138" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="F138" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G138" s="10"/>
-      <c r="H138" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="13">
-      <c r="A139" s="12">
-        <f t="shared" si="1"/>
+      <c r="F138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="13">
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="D139" s="13" t="s">
+      <c r="D139" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="E139" s="13" t="s">
+      <c r="E139" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="F139" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G139" s="10"/>
-      <c r="H139" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="13">
-      <c r="A140" s="12">
-        <f t="shared" si="1"/>
+      <c r="F139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="13">
+        <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C140" s="13" t="s">
+      <c r="C140" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="D140" s="13" t="s">
+      <c r="D140" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="E140" s="13" t="s">
+      <c r="E140" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="F140" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G140" s="10"/>
-      <c r="H140" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" ht="13">
-      <c r="A141" s="12">
-        <f t="shared" si="1"/>
+      <c r="F140" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="13">
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C141" s="13" t="s">
+      <c r="C141" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D141" s="13" t="s">
+      <c r="D141" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E141" s="13" t="s">
+      <c r="E141" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="F141" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="10"/>
-      <c r="H141" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="13">
-      <c r="A142" s="12">
-        <f t="shared" si="1"/>
+      <c r="F141" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="13">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C142" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="D142" s="13" t="s">
+      <c r="D142" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="E142" s="13" t="s">
+      <c r="E142" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F142" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="13">
-      <c r="A143" s="12">
-        <f t="shared" si="1"/>
+      <c r="F142" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="13">
+        <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D143" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="E143" s="13" t="s">
+      <c r="E143" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G143" s="10"/>
-      <c r="H143" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="13">
-      <c r="A144" s="12">
-        <f t="shared" si="1"/>
+      <c r="F143" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="13">
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="B144" s="13" t="s">
+      <c r="B144" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D144" s="13" t="s">
+      <c r="D144" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="E144" s="13" t="s">
+      <c r="E144" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="F144" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G144" s="10"/>
-      <c r="H144" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="13">
-      <c r="A145" s="12">
-        <f t="shared" si="1"/>
+      <c r="F144" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="13">
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="E145" s="13" t="s">
+      <c r="E145" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="F145" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="10"/>
-      <c r="H145" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="13">
-      <c r="A146" s="12">
-        <f t="shared" si="1"/>
+      <c r="F145" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="13">
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="C146" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="D146" s="13" t="s">
+      <c r="D146" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="E146" s="13" t="s">
+      <c r="E146" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="F146" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G146" s="10"/>
-      <c r="H146" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="13">
-      <c r="A147" s="12">
-        <f t="shared" si="1"/>
+      <c r="F146" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="13">
+        <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="C147" s="13" t="s">
+      <c r="C147" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="D147" s="13" t="s">
+      <c r="D147" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="E147" s="13" t="s">
+      <c r="E147" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="F147" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" s="10"/>
-      <c r="H147" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="13">
-      <c r="A148" s="12">
-        <f t="shared" si="1"/>
+      <c r="F147" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="13">
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="C148" s="13" t="s">
+      <c r="C148" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D148" s="13" t="s">
+      <c r="D148" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="E148" s="13" t="s">
+      <c r="E148" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="F148" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G148" s="10"/>
-      <c r="H148" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="13">
-      <c r="A149" s="12">
-        <f t="shared" si="1"/>
+      <c r="F148" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="13">
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C149" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D149" s="13" t="s">
+      <c r="D149" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="E149" s="13" t="s">
+      <c r="E149" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="F149" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G149" s="10"/>
-      <c r="H149" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="13">
-      <c r="A150" s="12">
-        <f t="shared" si="1"/>
+      <c r="F149" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="11"/>
+      <c r="H149" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="13">
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C150" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D150" s="13" t="s">
+      <c r="D150" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E150" s="13" t="s">
+      <c r="E150" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="F150" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G150" s="10"/>
-      <c r="H150" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="13">
-      <c r="A151" s="12">
-        <f t="shared" si="1"/>
+      <c r="F150" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="11"/>
+      <c r="H150" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="13">
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C151" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D151" s="13" t="s">
+      <c r="D151" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="E151" s="13" t="s">
+      <c r="E151" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="F151" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G151" s="10"/>
-      <c r="H151" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="13">
-      <c r="A152" s="12">
-        <f t="shared" si="1"/>
+      <c r="F151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G151" s="11"/>
+      <c r="H151" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="13">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="C152" s="13" t="s">
+      <c r="C152" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="D152" s="13" t="s">
+      <c r="D152" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="E152" s="13" t="s">
+      <c r="E152" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="F152" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G152" s="10"/>
-      <c r="H152" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="13">
-      <c r="A153" s="12">
-        <f t="shared" si="1"/>
+      <c r="F152" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="11"/>
+      <c r="H152" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="13">
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B153" s="13" t="s">
+      <c r="B153" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C153" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="D153" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="E153" s="13" t="s">
+      <c r="E153" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="F153" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G153" s="10"/>
-      <c r="H153" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="13">
-      <c r="F154" s="10"/>
-      <c r="G154" s="10"/>
-      <c r="H154" s="10"/>
-    </row>
-    <row r="155" spans="1:8" ht="13">
-      <c r="F155" s="10"/>
-      <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
-    </row>
-    <row r="156" spans="1:8" ht="13">
-      <c r="F156" s="10"/>
-      <c r="G156" s="10"/>
-      <c r="H156" s="10"/>
-    </row>
-    <row r="157" spans="1:8" ht="13">
-      <c r="F157" s="10"/>
-      <c r="G157" s="10"/>
-      <c r="H157" s="10"/>
-    </row>
-    <row r="158" spans="1:8" ht="13">
-      <c r="F158" s="10"/>
-      <c r="G158" s="10"/>
-      <c r="H158" s="10"/>
-    </row>
-    <row r="159" spans="1:8" ht="13">
-      <c r="F159" s="10"/>
-      <c r="G159" s="10"/>
-      <c r="H159" s="10"/>
-    </row>
-    <row r="160" spans="1:8" ht="13">
-      <c r="F160" s="10"/>
-      <c r="G160" s="10"/>
-      <c r="H160" s="10"/>
-    </row>
-    <row r="161" spans="6:8" ht="13">
-      <c r="F161" s="10"/>
-      <c r="G161" s="10"/>
-      <c r="H161" s="10"/>
-    </row>
+      <c r="F153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="E154" s="15"/>
+      <c r="F154" s="15"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="11"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="E155" s="15"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="11"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="E156" s="15"/>
+      <c r="F156" s="15"/>
+      <c r="G156" s="16"/>
+      <c r="H156" s="11"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="17"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="18"/>
+      <c r="D157" s="18"/>
+      <c r="E157" s="19"/>
+      <c r="F157" s="15"/>
+      <c r="G157" s="16"/>
+      <c r="H157" s="11"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="20">
+        <v>72.0</v>
+      </c>
+      <c r="B158" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D158" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="E158" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="F158" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" s="22"/>
+      <c r="H158" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="20">
+        <v>73.0</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="D159" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="E159" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="F159" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G159" s="22"/>
+      <c r="H159" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="20">
+        <v>74.0</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="22"/>
+      <c r="H160" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="20">
+        <v>75.0</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="D161" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="E161" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="F161" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G161" s="22"/>
+      <c r="H161" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="20">
+        <v>76.0</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="22"/>
+      <c r="H162" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="20">
+        <v>77.0</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="D163" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E163" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="F163" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" s="22"/>
+      <c r="H163" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="20">
+        <v>78.0</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="C164" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="D164" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E164" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F164" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" s="22"/>
+      <c r="H164" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="20">
+        <v>79.0</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="22"/>
+      <c r="H165" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="20">
+        <v>80.0</v>
+      </c>
+      <c r="B166" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C166" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D166" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="E166" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="22"/>
+      <c r="H166" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="20">
+        <v>81.0</v>
+      </c>
+      <c r="B167" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C167" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D167" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="E167" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="F167" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="22"/>
+      <c r="H167" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="20">
+        <v>82.0</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C168" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="D168" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="E168" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="F168" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="22"/>
+      <c r="H168" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="25">
+        <v>83.0</v>
+      </c>
+      <c r="B169" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C169" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="D169" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="E169" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="F169" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G169" s="27"/>
+      <c r="H169" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="28"/>
+      <c r="B170" s="17"/>
+      <c r="C170" s="17"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="15"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="D171" s="29"/>
+      <c r="E171" s="15"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="D172" s="29"/>
+      <c r="E172" s="15"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="30">
+        <v>84.0</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="C173" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="E173" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="F173" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="19"/>
+      <c r="H173" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I173" s="32"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="30">
+        <v>85.0</v>
+      </c>
+      <c r="B174" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="C174" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="E174" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="F174" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="19"/>
+      <c r="H174" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I174" s="32"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="30">
+        <v>86.0</v>
+      </c>
+      <c r="B175" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="E175" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="F175" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" s="19"/>
+      <c r="H175" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I175" s="32"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="30">
+        <v>87.0</v>
+      </c>
+      <c r="B176" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="C176" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="E176" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="F176" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="19"/>
+      <c r="H176" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I176" s="32"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="30">
+        <v>88.0</v>
+      </c>
+      <c r="B177" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="E177" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="F177" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="19"/>
+      <c r="H177" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I177" s="32"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="30">
+        <v>89.0</v>
+      </c>
+      <c r="B178" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="C178" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="E178" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="F178" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="19"/>
+      <c r="H178" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178" s="32"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="30">
+        <v>90.0</v>
+      </c>
+      <c r="B179" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="E179" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="F179" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="19"/>
+      <c r="H179" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I179" s="32"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="30">
+        <v>91.0</v>
+      </c>
+      <c r="B180" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="C180" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E180" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="F180" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G180" s="19"/>
+      <c r="H180" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I180" s="32"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="30">
+        <v>92.0</v>
+      </c>
+      <c r="B181" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C181" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="E181" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="F181" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="19"/>
+      <c r="H181" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I181" s="32"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="30">
+        <v>93.0</v>
+      </c>
+      <c r="B182" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="C182" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="D182" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="E182" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="F182" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" s="19"/>
+      <c r="H182" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I182" s="32"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="30">
+        <v>94.0</v>
+      </c>
+      <c r="B183" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="C183" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="D183" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="E183" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="F183" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G183" s="19"/>
+      <c r="H183" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I183" s="32"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="30">
+        <v>95.0</v>
+      </c>
+      <c r="B184" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="C184" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="E184" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="F184" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G184" s="19"/>
+      <c r="H184" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I184" s="32"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="30">
+        <v>96.0</v>
+      </c>
+      <c r="B185" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="C185" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E185" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="F185" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G185" s="19"/>
+      <c r="H185" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I185" s="32"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="30">
+        <v>97.0</v>
+      </c>
+      <c r="B186" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="C186" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="D186" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="E186" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="F186" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="19"/>
+      <c r="H186" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I186" s="32"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="33">
+        <v>98.0</v>
+      </c>
+      <c r="B187" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="C187" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="D187" s="34" t="s">
+        <v>471</v>
+      </c>
+      <c r="E187" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="F187" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G187" s="34"/>
+      <c r="H187" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I187" s="17"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="D191" s="18"/>
+      <c r="E191" s="17"/>
+      <c r="F191" s="17"/>
+      <c r="G191" s="17"/>
+      <c r="H191" s="17"/>
+      <c r="I191" s="17"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="36">
+        <v>99.0</v>
+      </c>
+      <c r="B192" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="C192" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="D192" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="E192" s="37" t="s">
+        <v>476</v>
+      </c>
+      <c r="F192" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G192" s="37"/>
+      <c r="H192" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I192" s="39"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="36">
+        <v>100.0</v>
+      </c>
+      <c r="B193" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="C193" s="37" t="s">
+        <v>478</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="E193" s="37" t="s">
+        <v>480</v>
+      </c>
+      <c r="F193" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G193" s="37"/>
+      <c r="H193" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193" s="39"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="36">
+        <v>101.0</v>
+      </c>
+      <c r="B194" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="C194" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="D194" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="E194" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="F194" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" s="37"/>
+      <c r="H194" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I194" s="39"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="36">
+        <v>102.0</v>
+      </c>
+      <c r="B195" s="37" t="s">
+        <v>485</v>
+      </c>
+      <c r="C195" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="D195" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="E195" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="F195" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" s="37"/>
+      <c r="H195" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I195" s="39"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="36">
+        <v>103.0</v>
+      </c>
+      <c r="B196" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="C196" s="37" t="s">
+        <v>490</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="E196" s="37" t="s">
+        <v>492</v>
+      </c>
+      <c r="F196" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" s="37"/>
+      <c r="H196" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" s="39"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="36">
+        <v>104.0</v>
+      </c>
+      <c r="B197" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="C197" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="D197" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="E197" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="F197" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="37"/>
+      <c r="H197" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I197" s="39"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="36">
+        <v>105.0</v>
+      </c>
+      <c r="B198" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C198" s="37" t="s">
+        <v>498</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="E198" s="37" t="s">
+        <v>500</v>
+      </c>
+      <c r="F198" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G198" s="37"/>
+      <c r="H198" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I198" s="39"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="36">
+        <v>106.0</v>
+      </c>
+      <c r="B199" s="37" t="s">
+        <v>501</v>
+      </c>
+      <c r="C199" s="37" t="s">
+        <v>502</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="E199" s="37" t="s">
+        <v>504</v>
+      </c>
+      <c r="F199" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G199" s="37"/>
+      <c r="H199" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I199" s="39"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="36">
+        <v>107.0</v>
+      </c>
+      <c r="B200" s="37" t="s">
+        <v>505</v>
+      </c>
+      <c r="C200" s="37" t="s">
+        <v>506</v>
+      </c>
+      <c r="D200" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="E200" s="37" t="s">
+        <v>508</v>
+      </c>
+      <c r="F200" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G200" s="37"/>
+      <c r="H200" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I200" s="39"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="36">
+        <v>108.0</v>
+      </c>
+      <c r="B201" s="37" t="s">
+        <v>509</v>
+      </c>
+      <c r="C201" s="37" t="s">
+        <v>510</v>
+      </c>
+      <c r="D201" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="E201" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="F201" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G201" s="37"/>
+      <c r="H201" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I201" s="39"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="36">
+        <v>109.0</v>
+      </c>
+      <c r="B202" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="C202" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="D202" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="E202" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="F202" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G202" s="37"/>
+      <c r="H202" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I202" s="39"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="36">
+        <v>110.0</v>
+      </c>
+      <c r="B203" s="37" t="s">
+        <v>517</v>
+      </c>
+      <c r="C203" s="37" t="s">
+        <v>518</v>
+      </c>
+      <c r="D203" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="E203" s="40" t="s">
+        <v>520</v>
+      </c>
+      <c r="F203" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G203" s="37"/>
+      <c r="H203" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I203" s="39"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="36">
+        <v>111.0</v>
+      </c>
+      <c r="B204" s="37" t="s">
+        <v>521</v>
+      </c>
+      <c r="C204" s="37" t="s">
+        <v>522</v>
+      </c>
+      <c r="D204" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="E204" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="F204" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G204" s="37"/>
+      <c r="H204" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I204" s="39"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="36">
+        <v>112.0</v>
+      </c>
+      <c r="B205" s="37" t="s">
+        <v>525</v>
+      </c>
+      <c r="C205" s="37" t="s">
+        <v>526</v>
+      </c>
+      <c r="D205" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="E205" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="F205" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G205" s="37"/>
+      <c r="H205" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I205" s="39"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="41">
+        <v>113.0</v>
+      </c>
+      <c r="B206" s="42" t="s">
+        <v>529</v>
+      </c>
+      <c r="C206" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="D206" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="E206" s="40" t="s">
+        <v>532</v>
+      </c>
+      <c r="F206" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" s="42"/>
+      <c r="H206" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I206" s="43"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="44"/>
+      <c r="B207" s="17"/>
+      <c r="D207" s="18"/>
+      <c r="E207" s="45"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="46"/>
+      <c r="B208" s="17"/>
+      <c r="D208" s="18"/>
+      <c r="E208" s="45"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="D209" s="18"/>
+      <c r="E209" s="45"/>
+      <c r="H209" s="37"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="H210" s="37"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="H211" s="37"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="H212" s="37"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="H213" s="37"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>